--- a/Catch and index models/JABBA_macarellus/jabba_cenarios_racional.xlsx
+++ b/Catch and index models/JABBA_macarellus/jabba_cenarios_racional.xlsx
@@ -118,7 +118,7 @@
     <t>range [3015, 92821] t (mediana 16729)</t>
   </si>
   <si>
-    <t>lnorm(0.90, CV 0.25) - estoque pouco explorado em 1989</t>
+    <t>lnorm(0.63, CV 0.19) - estoque pouco explorado em 1989</t>
   </si>
   <si>
     <t>J2_C2C3_nominal</t>
@@ -852,34 +852,34 @@
         <v>35</v>
       </c>
       <c r="N2">
-        <v>85.2</v>
+        <v>80.3</v>
       </c>
       <c r="O2">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="P2">
-        <v>-209.4</v>
+        <v>-213.6</v>
       </c>
       <c r="Q2">
         <v>2025</v>
       </c>
       <c r="R2">
-        <v>1.830534009177713</v>
+        <v>1.70348958600296</v>
       </c>
       <c r="S2">
-        <v>0.1912604116020698</v>
+        <v>0.146665623233057</v>
       </c>
       <c r="T2">
-        <v>2.164898897317832</v>
+        <v>2.146581839620756</v>
       </c>
       <c r="U2">
-        <v>0.009190571593477545</v>
+        <v>0.01301845724759509</v>
       </c>
       <c r="V2">
-        <v>0.9152670045888567</v>
+        <v>0.8517447930014801</v>
       </c>
       <c r="W2">
-        <v>0.2168</v>
+        <v>0.3862</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
@@ -926,34 +926,34 @@
         <v>35</v>
       </c>
       <c r="N3">
-        <v>67.7</v>
+        <v>65.8</v>
       </c>
       <c r="O3">
         <v>0.9399999999999999</v>
       </c>
       <c r="P3">
-        <v>-237.9</v>
+        <v>-241.1</v>
       </c>
       <c r="Q3">
         <v>2025</v>
       </c>
       <c r="R3">
-        <v>0.5315885289768161</v>
+        <v>0.6489144011979358</v>
       </c>
       <c r="S3">
-        <v>0.03929670830840837</v>
+        <v>0.03915061110766582</v>
       </c>
       <c r="T3">
-        <v>2.14083116798907</v>
+        <v>2.139709455488031</v>
       </c>
       <c r="U3">
-        <v>0.06270194325321241</v>
+        <v>0.05814654904107172</v>
       </c>
       <c r="V3">
-        <v>0.265794264488408</v>
+        <v>0.3244572005989679</v>
       </c>
       <c r="W3">
-        <v>0.5009</v>
+        <v>0.5</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
@@ -1000,34 +1000,34 @@
         <v>35</v>
       </c>
       <c r="N4">
-        <v>73.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O4">
         <v>1.01</v>
       </c>
       <c r="P4">
-        <v>-246.6</v>
+        <v>-247.5</v>
       </c>
       <c r="Q4">
         <v>2025</v>
       </c>
       <c r="R4">
-        <v>1.929321056339325</v>
+        <v>1.922106715040185</v>
       </c>
       <c r="S4">
-        <v>1.577961128762042</v>
+        <v>1.524317030127642</v>
       </c>
       <c r="T4">
-        <v>2.217742333063614</v>
+        <v>2.236556208237061</v>
       </c>
       <c r="U4">
-        <v>0.009636268409376321</v>
+        <v>0.01008927988372973</v>
       </c>
       <c r="V4">
-        <v>0.9646605281696623</v>
+        <v>0.9610533575200925</v>
       </c>
       <c r="W4">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
@@ -1115,34 +1115,34 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>127.1</v>
+        <v>94.2</v>
       </c>
       <c r="O6">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="P6">
-        <v>-284.4</v>
+        <v>-287.1</v>
       </c>
       <c r="Q6">
         <v>2025</v>
       </c>
       <c r="R6">
-        <v>1.932444738463548</v>
+        <v>0.6897639458397753</v>
       </c>
       <c r="S6">
-        <v>1.606854489392894</v>
+        <v>0.04064540455717738</v>
       </c>
       <c r="T6">
-        <v>2.212626288836562</v>
+        <v>2.147831872385696</v>
       </c>
       <c r="U6">
-        <v>0.008807426878858528</v>
+        <v>0.06110823484584641</v>
       </c>
       <c r="V6">
-        <v>0.9662223692317741</v>
+        <v>0.3448819729198876</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
@@ -1189,31 +1189,31 @@
         <v>35</v>
       </c>
       <c r="N7">
-        <v>73.8</v>
+        <v>73.5</v>
       </c>
       <c r="O7">
         <v>1.01</v>
       </c>
       <c r="P7">
-        <v>-247.2</v>
+        <v>-248.5</v>
       </c>
       <c r="Q7">
         <v>2025</v>
       </c>
       <c r="R7">
-        <v>2.616066387877068</v>
+        <v>2.613770362584439</v>
       </c>
       <c r="S7">
-        <v>2.200112257503482</v>
+        <v>2.250483826059567</v>
       </c>
       <c r="T7">
-        <v>3.011539756487755</v>
+        <v>2.971483094376627</v>
       </c>
       <c r="U7">
-        <v>0.005793501307970151</v>
+        <v>0.006078712828097373</v>
       </c>
       <c r="V7">
-        <v>0.9628780389608391</v>
+        <v>0.9620329563049033</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1263,34 +1263,34 @@
         <v>35</v>
       </c>
       <c r="N8">
-        <v>72.8</v>
+        <v>72</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>-244.1</v>
+        <v>-247.6</v>
       </c>
       <c r="Q8">
         <v>2025</v>
       </c>
       <c r="R8">
-        <v>1.863967829479363</v>
+        <v>1.866784333363605</v>
       </c>
       <c r="S8">
-        <v>1.282125986942569</v>
+        <v>1.30700038318275</v>
       </c>
       <c r="T8">
-        <v>2.232188244193045</v>
+        <v>2.213793342115664</v>
       </c>
       <c r="U8">
-        <v>0.0111684475418415</v>
+        <v>0.01160351952574101</v>
       </c>
       <c r="V8">
-        <v>0.9319839147396816</v>
+        <v>0.9333921666818026</v>
       </c>
       <c r="W8">
-        <v>0.0034</v>
+        <v>0.0078</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
@@ -1337,31 +1337,31 @@
         <v>35</v>
       </c>
       <c r="N9">
-        <v>73.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="O9">
         <v>1.01</v>
       </c>
       <c r="P9">
-        <v>-248.4</v>
+        <v>-249.2</v>
       </c>
       <c r="Q9">
         <v>2025</v>
       </c>
       <c r="R9">
-        <v>1.944723529694755</v>
+        <v>1.944175626174088</v>
       </c>
       <c r="S9">
-        <v>1.700278750442622</v>
+        <v>1.697340200008705</v>
       </c>
       <c r="T9">
-        <v>2.198995472833959</v>
+        <v>2.189377894024998</v>
       </c>
       <c r="U9">
-        <v>0.00890332053441022</v>
+        <v>0.009501654739291931</v>
       </c>
       <c r="V9">
-        <v>0.9723617648473777</v>
+        <v>0.972087813087044</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1411,34 +1411,34 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>127</v>
+        <v>126.6</v>
       </c>
       <c r="O10">
         <v>1.04</v>
       </c>
       <c r="P10">
-        <v>-283.8</v>
+        <v>-283.9</v>
       </c>
       <c r="Q10">
         <v>2025</v>
       </c>
       <c r="R10">
-        <v>1.925077181295874</v>
+        <v>1.924438693289885</v>
       </c>
       <c r="S10">
-        <v>1.610178072336476</v>
+        <v>1.608131546558765</v>
       </c>
       <c r="T10">
-        <v>2.190093821424485</v>
+        <v>2.198493926329923</v>
       </c>
       <c r="U10">
-        <v>0.008755874688049475</v>
+        <v>0.008275640038022447</v>
       </c>
       <c r="V10">
-        <v>0.9625385906479369</v>
+        <v>0.9622193466449426</v>
       </c>
       <c r="W10">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
@@ -1485,34 +1485,34 @@
         <v>35</v>
       </c>
       <c r="N11">
-        <v>66.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="O11">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <v>-236.6</v>
+        <v>-247.7</v>
       </c>
       <c r="Q11">
         <v>2025</v>
       </c>
       <c r="R11">
-        <v>0.8677861881438657</v>
+        <v>1.931658377597843</v>
       </c>
       <c r="S11">
-        <v>0.04243330003083043</v>
+        <v>1.704825655999558</v>
       </c>
       <c r="T11">
-        <v>2.116286594620069</v>
+        <v>2.163243386538205</v>
       </c>
       <c r="U11">
-        <v>0.03051581927421406</v>
+        <v>0.01251052914861576</v>
       </c>
       <c r="V11">
-        <v>0.4338930940719328</v>
+        <v>0.9658291887989217</v>
       </c>
       <c r="W11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
@@ -1559,34 +1559,34 @@
         <v>35</v>
       </c>
       <c r="N12">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="O12">
         <v>1.01</v>
       </c>
       <c r="P12">
-        <v>-248</v>
+        <v>-249.6</v>
       </c>
       <c r="Q12">
         <v>2025</v>
       </c>
       <c r="R12">
-        <v>1.940207361836288</v>
+        <v>1.944541440184515</v>
       </c>
       <c r="S12">
-        <v>1.557676207913088</v>
+        <v>1.63509788642728</v>
       </c>
       <c r="T12">
-        <v>2.25876568242976</v>
+        <v>2.207849729346932</v>
       </c>
       <c r="U12">
-        <v>0.005410062382364761</v>
+        <v>0.006107023415749842</v>
       </c>
       <c r="V12">
-        <v>0.9701036809181438</v>
+        <v>0.9722707200922578</v>
       </c>
       <c r="W12">
-        <v>0.0011</v>
+        <v>0.0001</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
@@ -1633,34 +1633,34 @@
         <v>25</v>
       </c>
       <c r="N13">
-        <v>71.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="O13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
-        <v>-262.7</v>
+        <v>-263.7</v>
       </c>
       <c r="Q13">
         <v>2025</v>
       </c>
       <c r="R13">
-        <v>1.939723513376226</v>
+        <v>1.933073278828853</v>
       </c>
       <c r="S13">
-        <v>1.622649826402579</v>
+        <v>1.591795681290496</v>
       </c>
       <c r="T13">
-        <v>2.25338640839254</v>
+        <v>2.239142030281299</v>
       </c>
       <c r="U13">
-        <v>0.008870204574006434</v>
+        <v>0.01031907657504531</v>
       </c>
       <c r="V13">
-        <v>0.9698617566881129</v>
+        <v>0.9665366394144266</v>
       </c>
       <c r="W13">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
@@ -1707,10 +1707,10 @@
         <v>35</v>
       </c>
       <c r="N14">
-        <v>77.5</v>
+        <v>67.5</v>
       </c>
       <c r="O14">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P14">
         <v>-244.1</v>
@@ -1719,22 +1719,22 @@
         <v>2025</v>
       </c>
       <c r="R14">
-        <v>1.921351323926983</v>
+        <v>0.613133927057994</v>
       </c>
       <c r="S14">
-        <v>1.510790134010157</v>
+        <v>0.03927838439680161</v>
       </c>
       <c r="T14">
-        <v>2.219554687075155</v>
+        <v>2.155038187393375</v>
       </c>
       <c r="U14">
-        <v>0.009527182025914963</v>
+        <v>0.09426992629016553</v>
       </c>
       <c r="V14">
-        <v>0.9606756619634916</v>
+        <v>0.306566963528997</v>
       </c>
       <c r="W14">
-        <v>0.0009</v>
+        <v>0.5</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
